--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M01/run_1/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M01/run_1/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.775</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7294</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.9062</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7838000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9747</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.9028</v>
       </c>
     </row>
@@ -1224,13 +1238,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>AWS RDS</t>
@@ -1254,13 +1266,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU35</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1306,13 +1316,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Web platform interface</t>
@@ -1336,13 +1344,11 @@
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU08</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1388,13 +1394,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>SQL database</t>
@@ -1418,13 +1422,11 @@
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1470,13 +1472,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -1500,13 +1500,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1527,7 +1525,6 @@
       <c r="D6" t="n">
         <v>0.8801</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1548,7 +1545,6 @@
           <t>['AU_07', 'AU_09']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_41</t>
@@ -1559,7 +1555,6 @@
           <t>waapiti web platform interface, api gateway</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1578,7 +1573,6 @@
           <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU25</t>
@@ -1609,7 +1603,6 @@
       <c r="D7" t="n">
         <v>0.9256</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1630,7 +1623,6 @@
           <t>['AU_03', 'AU_09']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_40</t>
@@ -1641,7 +1633,6 @@
           <t>presentation layer, api gateway</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1660,7 +1651,6 @@
           <t>CF_M01_AU01, CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_AU24</t>
@@ -1716,13 +1706,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Waapiti Mobile Platform</t>
@@ -1746,13 +1734,11 @@
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU09</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1798,13 +1784,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -1828,13 +1812,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1880,13 +1862,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -1910,13 +1890,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1962,13 +1940,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -1992,13 +1968,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2044,13 +2018,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Business Layer</t>
@@ -2074,13 +2046,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2126,13 +2096,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Data Layer</t>
@@ -2156,13 +2124,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2203,7 +2169,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2214,7 +2179,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -2238,13 +2202,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2290,13 +2252,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -2320,13 +2280,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2372,13 +2330,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2402,13 +2358,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M01_AU32</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2454,13 +2408,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_36</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Amazon Athena</t>
@@ -2484,13 +2436,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M01_AU20</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2536,13 +2486,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -2566,13 +2514,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2618,13 +2564,11 @@
           <t>['AU_40', 'AU_41']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2648,13 +2592,11 @@
           <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M01_AU03</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2695,14 +2637,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2726,13 +2665,11 @@
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2773,14 +2710,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2804,13 +2738,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2856,13 +2788,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -2886,13 +2816,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2938,13 +2866,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2968,13 +2894,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3020,13 +2944,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_37</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>AWS Glue</t>
@@ -3050,13 +2972,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M01_AU21</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3102,13 +3022,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Analytical module</t>
@@ -3132,13 +3050,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M01_AU12</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3184,13 +3100,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Server</t>
@@ -3214,13 +3128,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3266,13 +3178,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_38</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Kinesis Data Streams</t>
@@ -3298,13 +3208,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M01_AU22</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3345,14 +3253,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3371,14 +3276,11 @@
       <c r="P28" t="n">
         <v>41</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3419,14 +3321,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -3450,13 +3349,11 @@
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M01_AU34</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3502,13 +3399,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>AWS cloud services set</t>
@@ -3534,13 +3429,11 @@
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3586,13 +3479,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_39</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Kinesis Data Firehose</t>
@@ -3616,13 +3507,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3668,13 +3557,11 @@
           <t>['AU_42']</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>AU_28</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -3698,13 +3585,11 @@
           <t>CF_M01_AU26</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>CF_M01_AU31</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3778,7 +3663,6 @@
           <t>Waapiti web platform interface</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>En aquest projecte, és la interfície visual de la plataforma de Waapiti.</t>
@@ -3814,7 +3698,6 @@
           <t>API Gateway</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Com es pot veure, l’únic component que interactua de manera directa amb la capa de presentació és el mòdul Api Gateway.</t>
@@ -3850,7 +3733,6 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Aquests components vindrien a ser, l’Api Gateway, el Core i el mòdul analític.</t>
@@ -3886,7 +3768,6 @@
           <t>Analytical module</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Mòdul analític: Aquest servei és el servei que s’ha començat a desenvolupar durant el desenvolupament d’aquest TFG.</t>
@@ -3922,7 +3803,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Conjunt de serveis cloud AWS: L’objectiu d’aquests serveis és formar un data lake on s’emmagatzemi tots els històrics per poder processar-los en el mòdul analític.</t>
@@ -3958,7 +3838,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Com a framework es farà ús de NestJS [2], amb el llenguatge Typescript [3], i per la infraestructura es farà ús dels serveis cloud d’AWS [4].</t>
@@ -3994,7 +3873,6 @@
           <t>NodeJS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Aquest framework és un framework de NodeJS que té com a funció principal la creació d’aplicacions de backend.</t>
@@ -4030,7 +3908,6 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Aquest llenguatge de programació que està construït a un nivell superior de JavaScript, és a dir, que estén la sintaxi de JavaScript.</t>
@@ -4066,7 +3943,6 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET per poder desenvolupar la infraestructura creant l’aplicació d’AWS CDK.</t>
@@ -4102,7 +3978,6 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET per poder desenvolupar la infraestructura creant l’aplicació d’AWS CDK.</t>
@@ -4138,7 +4013,6 @@
           <t>C#/.NET</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET per poder desenvolupar la infraestructura creant l’aplicació d’AWS CDK.</t>
@@ -4174,7 +4048,6 @@
           <t>AWS Cloud Development Kit (CDK)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Per poder desenvolupar toda la infraestructura necessària per al projecte s’ha fet ús de l’AWS Cloud Development, també anomenat AWS CDK.</t>
@@ -4210,7 +4083,6 @@
           <t>AWS CloudFormation</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>AWS CloudFormation [34] és un servei d’Amazon que ajuda a configurar els recursos d’AWS.</t>
@@ -4241,7 +4113,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>api gateway, core service</t>
@@ -4257,7 +4128,6 @@
           <t>CF_M01_AU24</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0.7455000000000001</v>
       </c>
@@ -4334,7 +4204,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
@@ -4370,7 +4239,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -4401,7 +4269,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -4437,7 +4304,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>api gateway service, core service, analytical module</t>
@@ -4473,7 +4339,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>player, api player</t>
@@ -4509,7 +4374,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>player, web socket</t>
@@ -4545,7 +4409,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>analytical module, aws cloud services set, sql database</t>
@@ -4581,7 +4444,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>core service, sql database, aws cloud services set</t>
@@ -4622,7 +4484,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
